--- a/data/trans_bre/P3A_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R2-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,18</t>
+          <t>-1,73; 1,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 1,69</t>
+          <t>-2,37; 2,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,62</t>
+          <t>-0,81; 2,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,16</t>
+          <t>-1,87; 2,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-58,41; 83,21</t>
+          <t>-59,81; 91,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,41; 49,54</t>
+          <t>-44,9; 65,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,25; 199,19</t>
+          <t>-37,06; 211,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 42,46</t>
+          <t>-25,05; 47,78</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,56; -0,59</t>
+          <t>-3,67; -0,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,73</t>
+          <t>-2,06; 1,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,0</t>
+          <t>-1,12; 1,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,06</t>
+          <t>0,41; 4,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-76,82; -15,6</t>
+          <t>-77,52; -13,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,8; 52,52</t>
+          <t>-39,22; 48,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,19; 133,88</t>
+          <t>-41,01; 106,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,35; 238,52</t>
+          <t>7,5; 231,04</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,9</t>
+          <t>-2,45; 1,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,35</t>
+          <t>-0,33; 3,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,97</t>
+          <t>-1,49; 1,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,23</t>
+          <t>-2,94; 1,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 79,2</t>
+          <t>-51,15; 62,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 224,67</t>
+          <t>-15,94; 216,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-47,73; 132,81</t>
+          <t>-47,85; 132,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-54,09; 71,28</t>
+          <t>-56,16; 61,34</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,04</t>
+          <t>-3,03; 1,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 3,87</t>
+          <t>-0,25; 3,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,61</t>
+          <t>-0,93; 2,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,08</t>
+          <t>-1,09; 2,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,15; 21,07</t>
+          <t>-40,89; 26,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 107,36</t>
+          <t>-6,1; 104,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 104,13</t>
+          <t>-22,76; 106,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 72,46</t>
+          <t>-17,96; 65,05</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; -0,0</t>
+          <t>-1,84; 0,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,78</t>
+          <t>-0,28; 1,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,52</t>
+          <t>-0,18; 1,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 2,2</t>
+          <t>-0,11; 2,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-39,46; 1,25</t>
+          <t>-40,49; 1,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 53,72</t>
+          <t>-7,01; 54,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 73,74</t>
+          <t>-10,32; 65,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 60,26</t>
+          <t>-2,14; 61,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R2-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 1,35</t>
+          <t>-1,7; 1,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 2,15</t>
+          <t>-2,41; 1,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,7</t>
+          <t>-0,76; 2,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,46</t>
+          <t>-1,23; 2,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-59,81; 91,39</t>
+          <t>-59,15; 82,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,9; 65,94</t>
+          <t>-45,84; 64,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 211,84</t>
+          <t>-34,67; 227,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-25,05; 47,78</t>
+          <t>-16,92; 62,31</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,67; -0,43</t>
+          <t>-3,63; -0,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,55</t>
+          <t>-2,04; 1,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,72</t>
+          <t>-1,01; 1,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,24</t>
+          <t>-0,64; 2,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-77,52; -13,01</t>
+          <t>-77,89; -20,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,22; 48,48</t>
+          <t>-39,91; 46,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,01; 106,02</t>
+          <t>-39,54; 134,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 231,04</t>
+          <t>-15,26; 103,51</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,09%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,62</t>
+          <t>-2,26; 1,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,34</t>
+          <t>-0,33; 3,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,91</t>
+          <t>-1,43; 1,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,89</t>
+          <t>-0,84; 2,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-51,15; 62,78</t>
+          <t>-47,96; 65,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 216,54</t>
+          <t>-16,13; 217,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-47,85; 132,04</t>
+          <t>-47,12; 139,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-56,16; 61,34</t>
+          <t>-15,91; 104,99</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>1,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,33</t>
+          <t>-3,06; 1,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 3,61</t>
+          <t>-0,43; 3,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,6</t>
+          <t>-1,05; 2,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,77</t>
+          <t>-0,23; 3,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,89; 26,03</t>
+          <t>-43,12; 24,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 104,16</t>
+          <t>-8,28; 111,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 106,41</t>
+          <t>-25,08; 108,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 65,05</t>
+          <t>-4,06; 87,27</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,05</t>
+          <t>-1,9; -0,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,78</t>
+          <t>-0,23; 1,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,43</t>
+          <t>-0,19; 1,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,23</t>
+          <t>0,19; 2,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-40,49; 1,59</t>
+          <t>-40,95; -0,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 54,19</t>
+          <t>-5,08; 53,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 65,35</t>
+          <t>-7,53; 67,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 61,58</t>
+          <t>3,87; 54,63</t>
         </is>
       </c>
     </row>
